--- a/数据源/result_data_downWord.xlsx
+++ b/数据源/result_data_downWord.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="selected_120_images" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="626">
   <si>
     <t>vg_object_id</t>
   </si>
@@ -86,6 +86,12 @@
     <t>prompt</t>
   </si>
   <si>
+    <t>picture_id</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+  <si>
     <t>sheep</t>
   </si>
   <si>
@@ -113,30 +119,10 @@
     <t>male_child.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2348903_2298362_sheep.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2348903.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2348903_2298362_sheep.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2348903.jpg</t>
   </si>
   <si>
     <t>[55, 29, 164, 246]</t>
@@ -151,6 +137,9 @@
     <t>这是一____绵羊。</t>
   </si>
   <si>
+    <t>rdd-1</t>
+  </si>
+  <si>
     <t>cow</t>
   </si>
   <si>
@@ -175,17 +164,7 @@
     <t>ungulate.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2318362_3556707_cow.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2318362_3556707_cow.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2318362.jpg</t>
@@ -200,6 +179,9 @@
     <t>这是一____水牛。</t>
   </si>
   <si>
+    <t>rdd-2</t>
+  </si>
+  <si>
     <t>man</t>
   </si>
   <si>
@@ -227,30 +209,10 @@
     <t>woman.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2322860_3960187_tennis player.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2322860.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2322860_3960187_tennis player.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2322860.jpg</t>
   </si>
   <si>
     <t>[146, 76, 228, 405]</t>
@@ -262,6 +224,9 @@
     <t>这是一____网球运动员。</t>
   </si>
   <si>
+    <t>rdd-3</t>
+  </si>
+  <si>
     <t>kid</t>
   </si>
   <si>
@@ -286,17 +251,7 @@
     <t>child.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2328531_3273691_player.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2328531_3273691_player.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2328531.jpg</t>
@@ -308,6 +263,9 @@
     <t>这是一____篮球运动员。</t>
   </si>
   <si>
+    <t>rdd-4</t>
+  </si>
+  <si>
     <t>bird</t>
   </si>
   <si>
@@ -329,17 +287,7 @@
     <t>bird.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2329082_3110275_bird.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2329082_3110275_bird.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2329082.jpg</t>
@@ -351,6 +299,9 @@
     <t>这是一____灰雀。</t>
   </si>
   <si>
+    <t>rdd-5</t>
+  </si>
+  <si>
     <t>{'羊': 16, '羊羔': 1, '绵羊': 1, '羊肉': 1}</t>
   </si>
   <si>
@@ -363,17 +314,7 @@
     <t>2.694936842105263</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2338296_2637056_sheep.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2338296_2637056_sheep.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2338296.jpg</t>
@@ -382,6 +323,9 @@
     <t>[71, 164, 275, 145]</t>
   </si>
   <si>
+    <t>rdd-6</t>
+  </si>
+  <si>
     <t>puppy</t>
   </si>
   <si>
@@ -400,30 +344,10 @@
     <t>man.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2318417_3392338_bear.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2318417.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2318417_3392338_bear.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2318417.jpg</t>
   </si>
   <si>
     <t>[36, 79, 261, 254]</t>
@@ -432,6 +356,9 @@
     <t>这是一____黑熊。</t>
   </si>
   <si>
+    <t>rdd-7</t>
+  </si>
+  <si>
     <t>{'鸟': 14, '鹤': 3, '鹭': 1, '丹顶鹤': 1, '鸟类动物': 1, '鹳': 1}</t>
   </si>
   <si>
@@ -447,17 +374,7 @@
     <t>2.678305714285714</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2354530_2678297_bird.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2354530_2678297_bird.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2354530.jpg</t>
@@ -469,6 +386,9 @@
     <t>这是一____苍鹭。</t>
   </si>
   <si>
+    <t>rdd-8</t>
+  </si>
+  <si>
     <t>peacock</t>
   </si>
   <si>
@@ -487,30 +407,10 @@
     <t>4.261517391304348</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2354346_3777606_bird.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2354346.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2354346_3777606_bird.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2354346.jpg</t>
   </si>
   <si>
     <t>[21, 56, 146, 442]</t>
@@ -519,6 +419,9 @@
     <t>这是一____孔雀。</t>
   </si>
   <si>
+    <t>rdd-9</t>
+  </si>
+  <si>
     <t>{'bird': 27, 'parrot': 3, 'conure': 1}</t>
   </si>
   <si>
@@ -543,6 +446,9 @@
     <t>这是一____红鹦鹉。</t>
   </si>
   <si>
+    <t>rdd-10</t>
+  </si>
+  <si>
     <t>hen</t>
   </si>
   <si>
@@ -561,30 +467,10 @@
     <t>4.390160714285713</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2354864_834928_chicken.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2354864.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2354864_834928_chicken.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2354864.jpg</t>
   </si>
   <si>
     <t>[2, 1, 310, 497]</t>
@@ -593,6 +479,9 @@
     <t>这是一____土鸡。</t>
   </si>
   <si>
+    <t>rdd-11</t>
+  </si>
+  <si>
     <t>woman</t>
   </si>
   <si>
@@ -605,30 +494,10 @@
     <t>4.241851666666667</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2322480_3960820_soccer player.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2322480.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2322480_3960820_soccer player.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2322480.jpg</t>
   </si>
   <si>
     <t>[0, 83, 325, 417]</t>
@@ -637,6 +506,9 @@
     <t>这是一____足球运动员。</t>
   </si>
   <si>
+    <t>rdd-12</t>
+  </si>
+  <si>
     <t>dove</t>
   </si>
   <si>
@@ -658,30 +530,10 @@
     <t>2.729063157894737</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2405857_653443_bird.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2405857.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2405857_653443_bird.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2405857.jpg</t>
   </si>
   <si>
     <t>[88, 113, 341, 256]</t>
@@ -690,6 +542,9 @@
     <t>这是一____鸽子。</t>
   </si>
   <si>
+    <t>rdd-13</t>
+  </si>
+  <si>
     <t>pitcher</t>
   </si>
   <si>
@@ -708,17 +563,7 @@
     <t>athlete.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2415731_3627437_pitcher.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2415731_3627437_pitcher.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2415731.jpg</t>
@@ -730,6 +575,9 @@
     <t>这是一____棒球运动员。</t>
   </si>
   <si>
+    <t>rdd-14</t>
+  </si>
+  <si>
     <t>{'bird': 29, 'seagull': 4}</t>
   </si>
   <si>
@@ -751,6 +599,9 @@
     <t>这是一____海鸥。</t>
   </si>
   <si>
+    <t>rdd-15</t>
+  </si>
+  <si>
     <t>cat</t>
   </si>
   <si>
@@ -775,6 +626,9 @@
     <t>这是一____橘猫。</t>
   </si>
   <si>
+    <t>rdd-16</t>
+  </si>
+  <si>
     <t>flower</t>
   </si>
   <si>
@@ -793,17 +647,7 @@
     <t>flower.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2317946_2746869_flower.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2317946_2746869_flower.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2317946.jpg</t>
@@ -818,6 +662,9 @@
     <t>这是一____鸢尾花。</t>
   </si>
   <si>
+    <t>rdd-17</t>
+  </si>
+  <si>
     <t>{'羊': 14, '养': 1, '绵阳': 1}</t>
   </si>
   <si>
@@ -827,35 +674,18 @@
     <t>4.534666666666667</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2376480_2487758_sheep.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2376480.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2376480_2487758_sheep.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2376480.jpg</t>
   </si>
   <si>
     <t>[40, 91, 166, 283]</t>
   </si>
   <si>
+    <t>rdd-18</t>
+  </si>
+  <si>
     <t>{'花': 12, '花苞': 1, '菊花': 3, '花朵': 6}</t>
   </si>
   <si>
@@ -868,17 +698,7 @@
     <t>2.963972727272727</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2404668_1113936_flower.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2404668_1113936_flower.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2404668.jpg</t>
@@ -890,6 +710,9 @@
     <t>这是一____菊花。</t>
   </si>
   <si>
+    <t>rdd-19</t>
+  </si>
+  <si>
     <t>girl</t>
   </si>
   <si>
@@ -905,35 +728,18 @@
     <t>3.9629868421052623</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2339683_2333331_soccer player.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2339683.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2339683_2333331_soccer player.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2339683.jpg</t>
   </si>
   <si>
     <t>[0, 34, 212, 371]</t>
   </si>
   <si>
+    <t>rdd-20</t>
+  </si>
+  <si>
     <t>dog</t>
   </si>
   <si>
@@ -958,6 +764,9 @@
     <t>这是一____博美犬。</t>
   </si>
   <si>
+    <t>rdd-21</t>
+  </si>
+  <si>
     <t>{'鸟': 18, '老</t>
   </si>
   <si>
@@ -970,17 +779,7 @@
     <t>3.119819047619047</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2368044_2162294_bird.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2368044_2162294_bird.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2368044.jpg</t>
@@ -989,6 +788,9 @@
     <t>[213, 57, 167, 212]</t>
   </si>
   <si>
+    <t>rdd-22</t>
+  </si>
+  <si>
     <t>coat</t>
   </si>
   <si>
@@ -1004,30 +806,10 @@
     <t>4.116573913043478</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2395340_1206080_bear.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2395340.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2395340_1206080_bear.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2395340.jpg</t>
   </si>
   <si>
     <t>[179, 15, 269, 318]</t>
@@ -1036,23 +818,16 @@
     <t>这是一____棕熊。</t>
   </si>
   <si>
+    <t>rdd-23</t>
+  </si>
+  <si>
     <t>{'牛': 13, '鹿': 2, '驴': 1, '牛蹄子': 1, '奶牛': 2}</t>
   </si>
   <si>
     <t>2.1874175438596493</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2388537_672752_cow.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2388537_672752_cow.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2397176.jpg</t>
@@ -1064,6 +839,9 @@
     <t>这是一____黄牛。</t>
   </si>
   <si>
+    <t>rdd-24</t>
+  </si>
+  <si>
     <t>{'花': 20, '向日葵': 1}</t>
   </si>
   <si>
@@ -1076,17 +854,7 @@
     <t>3.859966666666667</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/265_1538388_flower.png</t>
-    </r>
+    <t>http://manynames.upf.edu/265_1538388_flower.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K_2/265.jpg</t>
@@ -1095,23 +863,16 @@
     <t>[69, 0, 407, 411]</t>
   </si>
   <si>
+    <t>rdd-25</t>
+  </si>
+  <si>
     <t>{'羊': 14, '山羊': 3, '绵羊': 1, '羊羔': 1, '动物': 1}</t>
   </si>
   <si>
     <t>1.419035274338866</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2387800_511037_sheep.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2387800_511037_sheep.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2387800.jpg</t>
@@ -1120,6 +881,9 @@
     <t>[17, 170, 266, 162]</t>
   </si>
   <si>
+    <t>rdd-26</t>
+  </si>
+  <si>
     <t>['狗']</t>
   </si>
   <si>
@@ -1132,30 +896,10 @@
     <t>4.035868421052632</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2331519_971735_dog.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2331519.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2331519_971735_dog.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2331519.jpg</t>
   </si>
   <si>
     <t>[192, 131, 706, 633]</t>
@@ -1164,6 +908,9 @@
     <t>这是一____拉布拉多。</t>
   </si>
   <si>
+    <t>rdd-27</t>
+  </si>
+  <si>
     <t>{'花': 17, '话': 1, '花瓣': 1, '假花': 1}</t>
   </si>
   <si>
@@ -1173,17 +920,7 @@
     <t>3.8601666666666654</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2332967_3024418_flower.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2332967_3024418_flower.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2332967.jpg</t>
@@ -1195,6 +932,9 @@
     <t>这是一____白菊。</t>
   </si>
   <si>
+    <t>rdd-28</t>
+  </si>
+  <si>
     <t>{'cat': 35, 'animal': 1}</t>
   </si>
   <si>
@@ -1219,6 +959,9 @@
     <t>这是一____狸花猫。</t>
   </si>
   <si>
+    <t>rdd-29</t>
+  </si>
+  <si>
     <t>{'人': 4, '网球选手': 1, '网球运动员': 3, '大人': 1, '打网球': 1, '运动员': 7, '球员': 1, '网球员': 1}</t>
   </si>
   <si>
@@ -1231,17 +974,7 @@
     <t>3.614494736842105</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2355614_2623413_player.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2355614_2623413_player.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/2355614.jpg</t>
@@ -1250,6 +983,9 @@
     <t>[182, 17, 258, 449]</t>
   </si>
   <si>
+    <t>rdd-30</t>
+  </si>
+  <si>
     <t>desk</t>
   </si>
   <si>
@@ -1286,6 +1022,9 @@
     <t>这是一____电脑桌。</t>
   </si>
   <si>
+    <t>rdd-31</t>
+  </si>
+  <si>
     <t>plane</t>
   </si>
   <si>
@@ -1301,17 +1040,7 @@
     <t>aircraft.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2338302_2416631_airplane.png</t>
-    </r>
+    <t>http://manynames.upf.edu/2338302_2416631_airplane.png</t>
   </si>
   <si>
     <t>[19, 110, 463, 158]</t>
@@ -1323,6 +1052,9 @@
     <t>这是一____客机。</t>
   </si>
   <si>
+    <t>rdd-32</t>
+  </si>
+  <si>
     <t>airplane</t>
   </si>
   <si>
@@ -1350,6 +1082,9 @@
     <t>这是一____战斗机。</t>
   </si>
   <si>
+    <t>rdd-33</t>
+  </si>
+  <si>
     <t>dress</t>
   </si>
   <si>
@@ -1389,6 +1124,9 @@
     <t>这是一____碎花裙。</t>
   </si>
   <si>
+    <t>rdd-34</t>
+  </si>
+  <si>
     <t>house.</t>
   </si>
   <si>
@@ -1413,17 +1151,7 @@
     <t>house.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/1592406_2377552_building.png</t>
-    </r>
+    <t>http://manynames.upf.edu/1592406_2377552_building.png</t>
   </si>
   <si>
     <t>https://cs.stanford.edu/people/rak248/VG_100K/1592406.jpg</t>
@@ -1438,6 +1166,9 @@
     <t>这是一____咖啡店。</t>
   </si>
   <si>
+    <t>rdd-35</t>
+  </si>
+  <si>
     <t>restaurant</t>
   </si>
   <si>
@@ -1471,6 +1202,9 @@
     <t>这是一____商店。</t>
   </si>
   <si>
+    <t>rdd-36</t>
+  </si>
+  <si>
     <t>bed</t>
   </si>
   <si>
@@ -1498,17 +1232,7 @@
     <t>http://manynames.upf.edu/2379457_552679_bed.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2379457.jpg</t>
-    </r>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K_2/2379457.jpg</t>
   </si>
   <si>
     <t>[0, 258, 499, 241]</t>
@@ -1517,6 +1241,9 @@
     <t>这是一____双人床。</t>
   </si>
   <si>
+    <t>rdd-37</t>
+  </si>
+  <si>
     <t>jet</t>
   </si>
   <si>
@@ -1535,6 +1262,9 @@
     <t>[186, 15, 312, 179]</t>
   </si>
   <si>
+    <t>rdd-38</t>
+  </si>
+  <si>
     <t>cake</t>
   </si>
   <si>
@@ -1562,6 +1292,9 @@
     <t>这是一____奶油蛋糕。</t>
   </si>
   <si>
+    <t>rdd-39</t>
+  </si>
+  <si>
     <t>['桌子']</t>
   </si>
   <si>
@@ -1583,6 +1316,9 @@
     <t>[0, 127, 678, 468]</t>
   </si>
   <si>
+    <t>rdd-40</t>
+  </si>
+  <si>
     <t>['婚纱']</t>
   </si>
   <si>
@@ -1607,6 +1343,9 @@
     <t>这是一____婚纱。</t>
   </si>
   <si>
+    <t>rdd-41</t>
+  </si>
+  <si>
     <t>['西装']</t>
   </si>
   <si>
@@ -1631,6 +1370,9 @@
     <t>这是一____西装。</t>
   </si>
   <si>
+    <t>rdd-42</t>
+  </si>
+  <si>
     <t>van</t>
   </si>
   <si>
@@ -1649,30 +1391,10 @@
     <t>truck.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2335906_961547_van.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2335906.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2335906_961547_van.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2335906.jpg</t>
   </si>
   <si>
     <t>[0, 0, 391, 158]</t>
@@ -1684,6 +1406,9 @@
     <t>这是一____巴士。</t>
   </si>
   <si>
+    <t>rdd-43</t>
+  </si>
+  <si>
     <t>jacket</t>
   </si>
   <si>
@@ -1705,6 +1430,9 @@
     <t>[0, 188, 338, 311]</t>
   </si>
   <si>
+    <t>rdd-44</t>
+  </si>
+  <si>
     <t>pizza</t>
   </si>
   <si>
@@ -1732,6 +1460,9 @@
     <t>这是一____披萨。</t>
   </si>
   <si>
+    <t>rdd-45</t>
+  </si>
+  <si>
     <t>knife</t>
   </si>
   <si>
@@ -1768,6 +1499,9 @@
     <t>这是一____折叠刀。</t>
   </si>
   <si>
+    <t>rdd-46</t>
+  </si>
+  <si>
     <t>pasta</t>
   </si>
   <si>
@@ -1792,6 +1526,9 @@
     <t>这是一____意大利面。</t>
   </si>
   <si>
+    <t>rdd-47</t>
+  </si>
+  <si>
     <t>truck</t>
   </si>
   <si>
@@ -1813,6 +1550,9 @@
     <t>[25, 45, 448, 279]</t>
   </si>
   <si>
+    <t>rdd-48</t>
+  </si>
+  <si>
     <t>counter</t>
   </si>
   <si>
@@ -1840,6 +1580,9 @@
     <t>这是一____橱柜。</t>
   </si>
   <si>
+    <t>rdd-49</t>
+  </si>
+  <si>
     <t>shirt</t>
   </si>
   <si>
@@ -1867,6 +1610,9 @@
     <t>这是一____短袖。</t>
   </si>
   <si>
+    <t>rdd-50</t>
+  </si>
+  <si>
     <t>outhouse</t>
   </si>
   <si>
@@ -1903,6 +1649,9 @@
     <t>这是一____厕所。</t>
   </si>
   <si>
+    <t>rdd-51</t>
+  </si>
+  <si>
     <t>boat</t>
   </si>
   <si>
@@ -1933,6 +1682,9 @@
     <t>这是一____帆船。</t>
   </si>
   <si>
+    <t>rdd-52</t>
+  </si>
+  <si>
     <t>['裙子']</t>
   </si>
   <si>
@@ -1957,6 +1709,9 @@
     <t>这是一____裙子。</t>
   </si>
   <si>
+    <t>rdd-53</t>
+  </si>
+  <si>
     <t>{'刀': 18, '刀子': 2, '菜刀': 1}</t>
   </si>
   <si>
@@ -1978,6 +1733,9 @@
     <t>这是一____水果刀。</t>
   </si>
   <si>
+    <t>rdd-54</t>
+  </si>
+  <si>
     <t>table</t>
   </si>
   <si>
@@ -2005,6 +1763,9 @@
     <t>这是一____酒桌。</t>
   </si>
   <si>
+    <t>rdd-55</t>
+  </si>
+  <si>
     <t>car</t>
   </si>
   <si>
@@ -2035,6 +1796,9 @@
     <t>这是一____皮卡。</t>
   </si>
   <si>
+    <t>rdd-56</t>
+  </si>
+  <si>
     <t>overpass</t>
   </si>
   <si>
@@ -2062,6 +1826,9 @@
     <t>这是一____高架桥</t>
   </si>
   <si>
+    <t>rdd-57</t>
+  </si>
+  <si>
     <t>['警车']</t>
   </si>
   <si>
@@ -2086,6 +1853,9 @@
     <t>这是一____警车。</t>
   </si>
   <si>
+    <t>rdd-58</t>
+  </si>
+  <si>
     <t>{'车': 11, '跑车': 4, '轿车': 3, '汽车': 3}</t>
   </si>
   <si>
@@ -2095,30 +1865,10 @@
     <t>boat.n.01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://manynames.upf.edu/2363195_767290_car.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://cs.stanford.edu/people/rak248/VG_100K/2363195.jpg</t>
-    </r>
+    <t>http://manynames.upf.edu/2363195_767290_car.png</t>
+  </si>
+  <si>
+    <t>https://cs.stanford.edu/people/rak248/VG_100K/2363195.jpg</t>
   </si>
   <si>
     <t>[0, 70, 220, 270]</t>
@@ -2127,6 +1877,9 @@
     <t>这是一____跑车。</t>
   </si>
   <si>
+    <t>rdd-59</t>
+  </si>
+  <si>
     <t>house</t>
   </si>
   <si>
@@ -2149,6 +1902,9 @@
   </si>
   <si>
     <t>这是一____铁棚。</t>
+  </si>
+  <si>
+    <t>rdd-60</t>
   </si>
 </sst>
 </file>
@@ -2619,165 +2375,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3313,13 +3064,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V61"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14"/>
+  <dimension ref="A1:W61"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="20" max="20" width="15.4545454545455" customWidth="1"/>
+    <col min="20" max="20" width="15.4537037037037" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3377,25 +3128,31 @@
       <c r="T1" t="s">
         <v>18</v>
       </c>
+      <c r="V1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>2298362</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
         <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -3404,57 +3161,63 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="N2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="P2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>3556707</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -3463,57 +3226,63 @@
         <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="O3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="T3" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="V3">
+        <v>2</v>
+      </c>
+      <c r="W3" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>3960187</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -3522,57 +3291,63 @@
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="P4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="R4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T4" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>3273691</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>9</v>
@@ -3581,57 +3356,63 @@
         <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M5" t="s">
-        <v>68</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T5" t="s">
-        <v>72</v>
+        <v>77</v>
+      </c>
+      <c r="V5">
+        <v>4</v>
+      </c>
+      <c r="W5" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>3110275</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -3640,57 +3421,63 @@
         <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="O6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="R6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T6" t="s">
-        <v>83</v>
+        <v>89</v>
+      </c>
+      <c r="V6">
+        <v>5</v>
+      </c>
+      <c r="W6" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>2637056</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -3699,57 +3486,63 @@
         <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>88</v>
+        <v>44</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="O7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="R7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>3392338</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -3761,54 +3554,60 @@
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L8">
         <v>4.24697</v>
       </c>
       <c r="M8" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="R8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T8" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V8">
+        <v>7</v>
+      </c>
+      <c r="W8" t="s">
+        <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>2678297</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -3817,57 +3616,63 @@
         <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J9" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="M9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="O9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="P9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="R9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T9" t="s">
-        <v>109</v>
+        <v>118</v>
+      </c>
+      <c r="V9">
+        <v>8</v>
+      </c>
+      <c r="W9" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>3777606</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -3876,57 +3681,63 @@
         <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="J10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L10" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>117</v>
+        <v>59</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="P10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="R10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T10" t="s">
-        <v>119</v>
+        <v>129</v>
+      </c>
+      <c r="V10">
+        <v>9</v>
+      </c>
+      <c r="W10" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>146131</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -3935,60 +3746,63 @@
         <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="J11" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L11" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="M11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>125</v>
+        <v>59</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="P11" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="R11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T11" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="W11" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>834928</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -3997,57 +3811,63 @@
         <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J12" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>135</v>
+        <v>59</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="P12" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="R12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T12" t="s">
-        <v>137</v>
+        <v>149</v>
+      </c>
+      <c r="V12">
+        <v>11</v>
+      </c>
+      <c r="W12" t="s">
+        <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>3960820</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>7</v>
@@ -4059,54 +3879,60 @@
         <v>40</v>
       </c>
       <c r="J13" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s">
-        <v>55</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>143</v>
+        <v>59</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="P13" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="R13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T13" t="s">
-        <v>145</v>
+        <v>158</v>
+      </c>
+      <c r="V13">
+        <v>12</v>
+      </c>
+      <c r="W13" t="s">
+        <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>653443</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -4115,57 +3941,63 @@
         <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J14" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="K14" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s">
-        <v>41</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>154</v>
+        <v>44</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="R14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T14" t="s">
-        <v>156</v>
+        <v>170</v>
+      </c>
+      <c r="V14">
+        <v>13</v>
+      </c>
+      <c r="W14" t="s">
+        <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>3627437</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -4174,57 +4006,63 @@
         <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="J15" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="K15" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s">
-        <v>162</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>163</v>
+        <v>177</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="O15" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="R15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T15" t="s">
-        <v>166</v>
+        <v>181</v>
+      </c>
+      <c r="V15">
+        <v>14</v>
+      </c>
+      <c r="W15" t="s">
+        <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>226061</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -4233,60 +4071,63 @@
         <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="J16" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s">
-        <v>79</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>171</v>
+        <v>85</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="R16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T16" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="V16">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="W16" t="s">
+        <v>190</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:23">
       <c r="A17">
         <v>173748</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -4298,57 +4139,60 @@
         <v>40</v>
       </c>
       <c r="J17" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="K17" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L17" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>179</v>
+        <v>59</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="P17" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="R17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T17" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="V17">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="W17" t="s">
+        <v>199</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>2746869</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -4357,57 +4201,63 @@
         <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="J18" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="K18" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L18">
         <v>3.9517</v>
       </c>
       <c r="M18" t="s">
-        <v>187</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="O18" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="P18" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="R18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S18" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="T18" t="s">
-        <v>192</v>
+        <v>210</v>
+      </c>
+      <c r="V18">
+        <v>17</v>
+      </c>
+      <c r="W18" t="s">
+        <v>211</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:23">
       <c r="A19">
         <v>2487758</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G19">
         <v>4</v>
@@ -4419,54 +4269,60 @@
         <v>45</v>
       </c>
       <c r="J19" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>197</v>
+        <v>104</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="R19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T19" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="V19">
+        <v>18</v>
+      </c>
+      <c r="W19" t="s">
+        <v>218</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:23">
       <c r="A20">
         <v>1113936</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -4475,57 +4331,63 @@
         <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="J20" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="K20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L20" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s">
-        <v>187</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="O20" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="P20" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="R20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S20" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="T20" t="s">
-        <v>206</v>
+        <v>226</v>
+      </c>
+      <c r="V20">
+        <v>19</v>
+      </c>
+      <c r="W20" t="s">
+        <v>227</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:23">
       <c r="A21">
         <v>2333331</v>
       </c>
       <c r="B21" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G21">
         <v>9</v>
@@ -4534,57 +4396,63 @@
         <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="J21" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="K21" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L21" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s">
-        <v>96</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>213</v>
+        <v>104</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="P21" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="R21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T21" t="s">
-        <v>145</v>
+        <v>158</v>
+      </c>
+      <c r="V21">
+        <v>20</v>
+      </c>
+      <c r="W21" t="s">
+        <v>236</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:23">
       <c r="A22">
         <v>230996</v>
       </c>
       <c r="B22" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="E22" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -4593,60 +4461,63 @@
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="J22" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s">
-        <v>55</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>220</v>
+        <v>59</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="P22" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="R22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T22" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="V22">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="W22" t="s">
+        <v>245</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>2162294</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -4655,57 +4526,63 @@
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="J23" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="K23" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L23" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s">
-        <v>79</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>227</v>
+        <v>85</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="O23" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="P23" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="R23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T23" t="s">
-        <v>173</v>
+        <v>189</v>
+      </c>
+      <c r="V23">
+        <v>22</v>
+      </c>
+      <c r="W23" t="s">
+        <v>253</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:23">
       <c r="A24">
         <v>1206080</v>
       </c>
       <c r="B24" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -4714,57 +4591,63 @@
         <v>23</v>
       </c>
       <c r="I24" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="J24" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L24" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s">
-        <v>55</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>236</v>
+        <v>59</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="P24" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="R24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T24" t="s">
-        <v>238</v>
+        <v>262</v>
+      </c>
+      <c r="V24">
+        <v>23</v>
+      </c>
+      <c r="W24" t="s">
+        <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:23">
       <c r="A25">
         <v>672752</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G25">
         <v>4</v>
@@ -4773,57 +4656,63 @@
         <v>19</v>
       </c>
       <c r="I25" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" t="s">
+        <v>93</v>
+      </c>
+      <c r="K25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L25" t="s">
+        <v>265</v>
+      </c>
+      <c r="M25" t="s">
         <v>85</v>
       </c>
-      <c r="J25" t="s">
-        <v>86</v>
-      </c>
-      <c r="K25" t="s">
-        <v>151</v>
-      </c>
-      <c r="L25" t="s">
-        <v>240</v>
-      </c>
-      <c r="M25" t="s">
-        <v>79</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>241</v>
+      <c r="N25" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="O25" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="P25" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="R25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S25" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="T25" t="s">
-        <v>244</v>
+        <v>269</v>
+      </c>
+      <c r="V25">
+        <v>24</v>
+      </c>
+      <c r="W25" t="s">
+        <v>270</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:23">
       <c r="A26">
         <v>1538388</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -4832,57 +4721,63 @@
         <v>21</v>
       </c>
       <c r="I26" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="J26" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="K26" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L26" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s">
-        <v>187</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>249</v>
+        <v>205</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="O26" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="P26" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="R26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S26" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="T26" t="s">
-        <v>206</v>
+        <v>226</v>
+      </c>
+      <c r="V26">
+        <v>25</v>
+      </c>
+      <c r="W26" t="s">
+        <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:23">
       <c r="A27">
         <v>511037</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -4894,54 +4789,60 @@
         <v>70</v>
       </c>
       <c r="J27" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="K27" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L27">
         <v>2.72666</v>
       </c>
       <c r="M27" t="s">
-        <v>41</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>254</v>
+        <v>44</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="O27" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="R27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S27" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="T27" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="V27">
+        <v>26</v>
+      </c>
+      <c r="W27" t="s">
+        <v>284</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:23">
       <c r="A28">
         <v>971735</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="E28" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G28">
         <v>6</v>
@@ -4950,57 +4851,63 @@
         <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="J28" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="K28" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L28" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s">
-        <v>55</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>262</v>
+        <v>59</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>290</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="R28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T28" t="s">
-        <v>264</v>
+        <v>292</v>
+      </c>
+      <c r="V28">
+        <v>27</v>
+      </c>
+      <c r="W28" t="s">
+        <v>293</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:23">
       <c r="A29">
         <v>3024418</v>
       </c>
       <c r="B29" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -5012,54 +4919,60 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="K29" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="M29" t="s">
-        <v>187</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>268</v>
+        <v>205</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="O29" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="P29" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="R29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S29" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="T29" t="s">
-        <v>271</v>
+        <v>300</v>
+      </c>
+      <c r="V29">
+        <v>28</v>
+      </c>
+      <c r="W29" t="s">
+        <v>301</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:23">
       <c r="A30">
         <v>256924</v>
       </c>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="E30" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G30">
         <v>9</v>
@@ -5068,60 +4981,63 @@
         <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="J30" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="K30" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L30" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s">
-        <v>27</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>277</v>
+        <v>29</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="P30" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="R30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T30" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="V30">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="W30" t="s">
+        <v>310</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:23">
       <c r="A31">
         <v>2623413</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -5130,57 +5046,63 @@
         <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="J31" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="K31" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L31" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s">
-        <v>96</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>284</v>
+        <v>104</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="O31" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="P31" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="R31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S31" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="T31" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="V31">
+        <v>30</v>
+      </c>
+      <c r="W31" t="s">
+        <v>318</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:23">
       <c r="A32">
         <v>264145</v>
       </c>
       <c r="B32" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="C32" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="E32" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F32" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -5189,60 +5111,63 @@
         <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="J32" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="K32" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L32" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="M32" t="s">
-        <v>293</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>294</v>
+        <v>325</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="P32" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="R32" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S32" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="T32" t="s">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="V32">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="W32" t="s">
+        <v>331</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:23">
       <c r="A33">
         <v>2416631</v>
       </c>
       <c r="B33" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
       <c r="C33" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="E33" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="F33" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -5257,51 +5182,57 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L33">
         <v>3.7007</v>
       </c>
       <c r="M33" t="s">
-        <v>303</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>304</v>
+        <v>336</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="P33" t="s">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="R33" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S33" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="T33" t="s">
-        <v>307</v>
+        <v>340</v>
+      </c>
+      <c r="V33">
+        <v>32</v>
+      </c>
+      <c r="W33" t="s">
+        <v>341</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:23">
       <c r="A34">
         <v>261223</v>
       </c>
       <c r="B34" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="C34" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="E34" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="F34" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G34">
         <v>9</v>
@@ -5310,60 +5241,63 @@
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="J34" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="K34" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L34" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="M34" t="s">
-        <v>313</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>314</v>
+        <v>347</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="P34" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="R34" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S34" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="T34" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="V34">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="W34" t="s">
+        <v>351</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:23">
       <c r="A35">
         <v>1113261</v>
       </c>
       <c r="B35" t="s">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="C35" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="D35" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="E35" t="s">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="F35" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -5372,57 +5306,63 @@
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>321</v>
+        <v>356</v>
       </c>
       <c r="J35" t="s">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="K35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L35" t="s">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="M35" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="N35" t="s">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="O35" t="s">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="P35" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="R35" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S35" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="T35" t="s">
-        <v>329</v>
+        <v>364</v>
+      </c>
+      <c r="V35">
+        <v>34</v>
+      </c>
+      <c r="W35" t="s">
+        <v>365</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:23">
       <c r="A36">
         <v>2377552</v>
       </c>
       <c r="B36" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="C36" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="D36" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="E36" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="F36" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -5431,57 +5371,63 @@
         <v>23</v>
       </c>
       <c r="I36" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="J36" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L36" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="M36" t="s">
-        <v>337</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>338</v>
+        <v>373</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="O36" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="P36" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="R36" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S36" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="T36" t="s">
-        <v>342</v>
+        <v>378</v>
+      </c>
+      <c r="V36">
+        <v>35</v>
+      </c>
+      <c r="W36" t="s">
+        <v>379</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:23">
       <c r="A37">
         <v>2177658</v>
       </c>
       <c r="B37" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="C37" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="D37" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="E37" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="F37" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="G37">
         <v>13</v>
@@ -5490,57 +5436,63 @@
         <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="J37" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="K37" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L37" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="N37" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="O37" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="P37" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="R37" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S37" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="T37" t="s">
-        <v>353</v>
+        <v>390</v>
+      </c>
+      <c r="V37">
+        <v>36</v>
+      </c>
+      <c r="W37" t="s">
+        <v>391</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:23">
       <c r="A38">
         <v>552679</v>
       </c>
       <c r="B38" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="C38" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="D38" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="E38" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="F38" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="G38">
         <v>9</v>
@@ -5549,57 +5501,63 @@
         <v>23</v>
       </c>
       <c r="I38" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="J38" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="K38" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L38" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="M38" t="s">
-        <v>361</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>363</v>
+        <v>399</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>401</v>
       </c>
       <c r="P38" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="R38" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S38" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="T38" t="s">
-        <v>365</v>
+        <v>403</v>
+      </c>
+      <c r="V38">
+        <v>37</v>
+      </c>
+      <c r="W38" t="s">
+        <v>404</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:23">
       <c r="A39">
         <v>2986259</v>
       </c>
       <c r="B39" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="C39" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="E39" t="s">
-        <v>367</v>
+        <v>406</v>
       </c>
       <c r="F39" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -5608,57 +5566,63 @@
         <v>21</v>
       </c>
       <c r="I39" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="J39" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="K39" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L39" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="M39" t="s">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="N39" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
       <c r="O39" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
       <c r="P39" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="R39" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S39" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="T39" t="s">
-        <v>316</v>
+        <v>350</v>
+      </c>
+      <c r="V39">
+        <v>38</v>
+      </c>
+      <c r="W39" t="s">
+        <v>411</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:23">
       <c r="A40">
         <v>273218</v>
       </c>
       <c r="B40" t="s">
-        <v>372</v>
+        <v>412</v>
       </c>
       <c r="C40" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="D40" t="s">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="E40" t="s">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="F40" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="G40">
         <v>6</v>
@@ -5667,60 +5631,63 @@
         <v>23</v>
       </c>
       <c r="I40" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="J40" t="s">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="K40" t="s">
+        <v>42</v>
+      </c>
+      <c r="L40" t="s">
+        <v>416</v>
+      </c>
+      <c r="M40" t="s">
+        <v>325</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="P40" t="s">
+        <v>418</v>
+      </c>
+      <c r="R40" t="s">
+        <v>328</v>
+      </c>
+      <c r="S40" t="s">
+        <v>419</v>
+      </c>
+      <c r="T40" t="s">
+        <v>420</v>
+      </c>
+      <c r="V40">
         <v>39</v>
       </c>
-      <c r="L40" t="s">
-        <v>376</v>
-      </c>
-      <c r="M40" t="s">
-        <v>293</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="P40" t="s">
-        <v>378</v>
-      </c>
-      <c r="R40" t="s">
-        <v>296</v>
-      </c>
-      <c r="S40" t="s">
-        <v>379</v>
-      </c>
-      <c r="T40" t="s">
-        <v>380</v>
-      </c>
-      <c r="V40">
-        <v>1</v>
+      <c r="W40" t="s">
+        <v>421</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:23">
       <c r="A41">
         <v>3789120</v>
       </c>
       <c r="B41" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="C41" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="D41" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="E41" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="F41" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="G41">
         <v>3</v>
@@ -5732,54 +5699,60 @@
         <v>80</v>
       </c>
       <c r="J41" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="K41" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="M41" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="N41" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="O41" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="P41" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="R41" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S41" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="T41" t="s">
-        <v>298</v>
+        <v>330</v>
+      </c>
+      <c r="V41">
+        <v>40</v>
+      </c>
+      <c r="W41" t="s">
+        <v>429</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:23">
       <c r="A42">
         <v>2403045</v>
       </c>
       <c r="B42" t="s">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="C42" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="D42" t="s">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="E42" t="s">
-        <v>389</v>
+        <v>431</v>
       </c>
       <c r="F42" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="G42">
         <v>7</v>
@@ -5791,54 +5764,60 @@
         <v>50</v>
       </c>
       <c r="J42" t="s">
-        <v>390</v>
+        <v>432</v>
       </c>
       <c r="K42" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L42" t="s">
-        <v>391</v>
+        <v>433</v>
       </c>
       <c r="M42" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="N42" t="s">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="O42" t="s">
-        <v>393</v>
+        <v>435</v>
       </c>
       <c r="P42" t="s">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="R42" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S42" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="T42" t="s">
-        <v>395</v>
+        <v>437</v>
+      </c>
+      <c r="V42">
+        <v>41</v>
+      </c>
+      <c r="W42" t="s">
+        <v>438</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:23">
       <c r="A43">
         <v>2146369</v>
       </c>
       <c r="B43" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C43" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="D43" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
       <c r="E43" t="s">
-        <v>397</v>
+        <v>440</v>
       </c>
       <c r="F43" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="G43">
         <v>7</v>
@@ -5850,54 +5829,60 @@
         <v>45</v>
       </c>
       <c r="J43" t="s">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="K43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L43">
         <v>2.722385</v>
       </c>
       <c r="M43" t="s">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="N43" t="s">
-        <v>400</v>
+        <v>443</v>
       </c>
       <c r="O43" t="s">
-        <v>401</v>
+        <v>444</v>
       </c>
       <c r="P43" t="s">
-        <v>402</v>
+        <v>445</v>
       </c>
       <c r="R43" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S43" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="T43" t="s">
-        <v>403</v>
+        <v>446</v>
+      </c>
+      <c r="V43">
+        <v>42</v>
+      </c>
+      <c r="W43" t="s">
+        <v>447</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:23">
       <c r="A44">
         <v>961547</v>
       </c>
       <c r="B44" t="s">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="C44" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D44" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="E44" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="F44" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G44">
         <v>8</v>
@@ -5906,57 +5891,63 @@
         <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="J44" t="s">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="K44" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="M44" t="s">
-        <v>409</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>411</v>
+        <v>453</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>455</v>
       </c>
       <c r="P44" t="s">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="R44" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S44" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="T44" t="s">
-        <v>414</v>
+        <v>458</v>
+      </c>
+      <c r="V44">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>459</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:23">
       <c r="A45">
         <v>1845057</v>
       </c>
       <c r="B45" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="C45" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="D45" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
       <c r="E45" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="F45" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="G45">
         <v>9</v>
@@ -5965,57 +5956,63 @@
         <v>21</v>
       </c>
       <c r="I45" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="J45" t="s">
-        <v>417</v>
+        <v>462</v>
       </c>
       <c r="K45" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L45" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
       <c r="M45" t="s">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="N45" t="s">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="O45" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="P45" t="s">
-        <v>421</v>
+        <v>466</v>
       </c>
       <c r="R45" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S45" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="T45" t="s">
-        <v>403</v>
+        <v>446</v>
+      </c>
+      <c r="V45">
+        <v>44</v>
+      </c>
+      <c r="W45" t="s">
+        <v>467</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:23">
       <c r="A46">
         <v>556533</v>
       </c>
       <c r="B46" t="s">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="C46" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="D46" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="E46" t="s">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="F46" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="G46">
         <v>5</v>
@@ -6027,54 +6024,60 @@
         <v>65</v>
       </c>
       <c r="J46" t="s">
-        <v>425</v>
+        <v>471</v>
       </c>
       <c r="K46" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L46">
         <v>2.437585</v>
       </c>
       <c r="M46" t="s">
-        <v>426</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>427</v>
+        <v>472</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>473</v>
       </c>
       <c r="O46" t="s">
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="P46" t="s">
-        <v>429</v>
+        <v>475</v>
       </c>
       <c r="R46" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S46" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="T46" t="s">
-        <v>430</v>
+        <v>476</v>
+      </c>
+      <c r="V46">
+        <v>45</v>
+      </c>
+      <c r="W46" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:23">
       <c r="A47">
         <v>3338224</v>
       </c>
       <c r="B47" t="s">
-        <v>431</v>
+        <v>478</v>
       </c>
       <c r="C47" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="D47" t="s">
-        <v>432</v>
+        <v>479</v>
       </c>
       <c r="E47" t="s">
-        <v>433</v>
+        <v>480</v>
       </c>
       <c r="F47" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -6083,57 +6086,63 @@
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>434</v>
+        <v>481</v>
       </c>
       <c r="J47" t="s">
-        <v>435</v>
+        <v>482</v>
       </c>
       <c r="K47" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L47" t="s">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="M47" t="s">
-        <v>437</v>
+        <v>484</v>
       </c>
       <c r="N47" t="s">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="O47" t="s">
-        <v>439</v>
+        <v>486</v>
       </c>
       <c r="P47" t="s">
-        <v>440</v>
+        <v>487</v>
       </c>
       <c r="R47" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S47" t="s">
-        <v>441</v>
+        <v>488</v>
       </c>
       <c r="T47" t="s">
-        <v>442</v>
+        <v>489</v>
+      </c>
+      <c r="V47">
+        <v>46</v>
+      </c>
+      <c r="W47" t="s">
+        <v>490</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:23">
       <c r="A48">
         <v>937444</v>
       </c>
       <c r="B48" t="s">
-        <v>443</v>
+        <v>491</v>
       </c>
       <c r="C48" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="D48" t="s">
-        <v>444</v>
+        <v>492</v>
       </c>
       <c r="E48" t="s">
-        <v>445</v>
+        <v>493</v>
       </c>
       <c r="F48" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -6142,60 +6151,63 @@
         <v>23</v>
       </c>
       <c r="I48" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="J48" t="s">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="K48" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L48" t="s">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="M48" t="s">
-        <v>293</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>447</v>
+        <v>325</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="P48" t="s">
-        <v>448</v>
+        <v>496</v>
       </c>
       <c r="R48" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S48" t="s">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="T48" t="s">
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="V48">
-        <v>1</v>
+        <v>47</v>
+      </c>
+      <c r="W48" t="s">
+        <v>499</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:23">
       <c r="A49">
         <v>914558</v>
       </c>
       <c r="B49" t="s">
-        <v>451</v>
+        <v>500</v>
       </c>
       <c r="C49" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D49" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="E49" t="s">
-        <v>452</v>
+        <v>501</v>
       </c>
       <c r="F49" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G49">
         <v>9</v>
@@ -6204,57 +6216,63 @@
         <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J49" t="s">
+        <v>502</v>
+      </c>
+      <c r="K49" t="s">
+        <v>27</v>
+      </c>
+      <c r="L49" t="s">
+        <v>503</v>
+      </c>
+      <c r="M49" t="s">
         <v>453</v>
       </c>
-      <c r="K49" t="s">
-        <v>25</v>
-      </c>
-      <c r="L49" t="s">
-        <v>454</v>
-      </c>
-      <c r="M49" t="s">
-        <v>409</v>
-      </c>
       <c r="N49" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="O49" t="s">
-        <v>456</v>
+        <v>505</v>
       </c>
       <c r="P49" t="s">
+        <v>506</v>
+      </c>
+      <c r="R49" t="s">
+        <v>328</v>
+      </c>
+      <c r="S49" t="s">
         <v>457</v>
       </c>
-      <c r="R49" t="s">
-        <v>296</v>
-      </c>
-      <c r="S49" t="s">
-        <v>413</v>
-      </c>
       <c r="T49" t="s">
-        <v>414</v>
+        <v>458</v>
+      </c>
+      <c r="V49">
+        <v>48</v>
+      </c>
+      <c r="W49" t="s">
+        <v>507</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:23">
       <c r="A50">
         <v>725035</v>
       </c>
       <c r="B50" t="s">
-        <v>458</v>
+        <v>508</v>
       </c>
       <c r="C50" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="D50" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="E50" t="s">
-        <v>459</v>
+        <v>509</v>
       </c>
       <c r="F50" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="G50">
         <v>7</v>
@@ -6263,57 +6281,63 @@
         <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="J50" t="s">
-        <v>461</v>
+        <v>511</v>
       </c>
       <c r="K50" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L50" t="s">
-        <v>462</v>
+        <v>512</v>
       </c>
       <c r="M50" t="s">
-        <v>313</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>463</v>
+        <v>347</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>513</v>
       </c>
       <c r="O50" t="s">
-        <v>464</v>
+        <v>514</v>
       </c>
       <c r="P50" t="s">
-        <v>465</v>
+        <v>515</v>
       </c>
       <c r="R50" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S50" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="T50" t="s">
-        <v>466</v>
+        <v>516</v>
+      </c>
+      <c r="V50">
+        <v>49</v>
+      </c>
+      <c r="W50" t="s">
+        <v>517</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:23">
       <c r="A51">
         <v>1351071</v>
       </c>
       <c r="B51" t="s">
-        <v>467</v>
+        <v>518</v>
       </c>
       <c r="C51" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="E51" t="s">
-        <v>468</v>
+        <v>519</v>
       </c>
       <c r="F51" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="G51">
         <v>7</v>
@@ -6322,57 +6346,63 @@
         <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J51" t="s">
-        <v>469</v>
+        <v>520</v>
       </c>
       <c r="K51" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L51" t="s">
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="M51" t="s">
-        <v>471</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>472</v>
+        <v>522</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>523</v>
       </c>
       <c r="O51" t="s">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="P51" t="s">
-        <v>474</v>
+        <v>525</v>
       </c>
       <c r="R51" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S51" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="T51" t="s">
-        <v>475</v>
+        <v>526</v>
+      </c>
+      <c r="V51">
+        <v>50</v>
+      </c>
+      <c r="W51" t="s">
+        <v>527</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:23">
       <c r="A52">
         <v>2119153</v>
       </c>
       <c r="B52" t="s">
-        <v>476</v>
+        <v>528</v>
       </c>
       <c r="C52" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="D52" t="s">
-        <v>477</v>
+        <v>529</v>
       </c>
       <c r="E52" t="s">
-        <v>478</v>
+        <v>530</v>
       </c>
       <c r="F52" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="G52">
         <v>7</v>
@@ -6381,57 +6411,63 @@
         <v>13</v>
       </c>
       <c r="I52" t="s">
-        <v>479</v>
+        <v>531</v>
       </c>
       <c r="J52" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="K52" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L52" t="s">
-        <v>481</v>
+        <v>533</v>
       </c>
       <c r="M52" t="s">
-        <v>482</v>
+        <v>534</v>
       </c>
       <c r="N52" t="s">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="O52" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="P52" t="s">
-        <v>485</v>
+        <v>537</v>
       </c>
       <c r="R52" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S52" t="s">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="T52" t="s">
-        <v>487</v>
+        <v>539</v>
+      </c>
+      <c r="V52">
+        <v>51</v>
+      </c>
+      <c r="W52" t="s">
+        <v>540</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:23">
       <c r="A53">
         <v>2075639</v>
       </c>
       <c r="B53" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="C53" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D53" t="s">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="E53" t="s">
-        <v>490</v>
+        <v>543</v>
       </c>
       <c r="F53" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G53">
         <v>8</v>
@@ -6440,57 +6476,63 @@
         <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="J53" t="s">
-        <v>491</v>
+        <v>544</v>
       </c>
       <c r="K53" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L53" t="s">
-        <v>492</v>
+        <v>545</v>
       </c>
       <c r="M53" t="s">
-        <v>493</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="O53" s="4" t="s">
-        <v>494</v>
+        <v>546</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>547</v>
       </c>
       <c r="P53" t="s">
-        <v>495</v>
+        <v>548</v>
       </c>
       <c r="R53" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S53" t="s">
-        <v>496</v>
+        <v>549</v>
       </c>
       <c r="T53" t="s">
-        <v>497</v>
+        <v>550</v>
+      </c>
+      <c r="V53">
+        <v>52</v>
+      </c>
+      <c r="W53" t="s">
+        <v>551</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:23">
       <c r="A54">
         <v>3324843</v>
       </c>
       <c r="B54" t="s">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="C54" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="D54" t="s">
-        <v>498</v>
+        <v>552</v>
       </c>
       <c r="E54" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="F54" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="G54">
         <v>7</v>
@@ -6502,54 +6544,60 @@
         <v>70</v>
       </c>
       <c r="J54" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
       <c r="K54" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L54" t="s">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="M54" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="N54" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="O54" t="s">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="P54" t="s">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="R54" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S54" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="T54" t="s">
-        <v>505</v>
+        <v>559</v>
+      </c>
+      <c r="V54">
+        <v>53</v>
+      </c>
+      <c r="W54" t="s">
+        <v>560</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:23">
       <c r="A55">
         <v>3749927</v>
       </c>
       <c r="B55" t="s">
-        <v>431</v>
+        <v>478</v>
       </c>
       <c r="C55" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="D55" t="s">
-        <v>432</v>
+        <v>479</v>
       </c>
       <c r="E55" t="s">
-        <v>506</v>
+        <v>561</v>
       </c>
       <c r="F55" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -6558,57 +6606,63 @@
         <v>21</v>
       </c>
       <c r="I55" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="J55" t="s">
-        <v>507</v>
+        <v>562</v>
       </c>
       <c r="K55" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L55" t="s">
-        <v>508</v>
+        <v>563</v>
       </c>
       <c r="M55" t="s">
-        <v>437</v>
+        <v>484</v>
       </c>
       <c r="N55" t="s">
-        <v>509</v>
+        <v>564</v>
       </c>
       <c r="O55" t="s">
-        <v>510</v>
+        <v>565</v>
       </c>
       <c r="P55" t="s">
-        <v>511</v>
+        <v>566</v>
       </c>
       <c r="R55" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S55" t="s">
-        <v>441</v>
+        <v>488</v>
       </c>
       <c r="T55" t="s">
-        <v>512</v>
+        <v>567</v>
+      </c>
+      <c r="V55">
+        <v>54</v>
+      </c>
+      <c r="W55" t="s">
+        <v>568</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:23">
       <c r="A56">
         <v>2071296</v>
       </c>
       <c r="B56" t="s">
-        <v>513</v>
+        <v>569</v>
       </c>
       <c r="C56" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="D56" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="E56" t="s">
-        <v>514</v>
+        <v>570</v>
       </c>
       <c r="F56" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="G56">
         <v>8</v>
@@ -6617,57 +6671,63 @@
         <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>515</v>
+        <v>571</v>
       </c>
       <c r="J56" t="s">
-        <v>516</v>
+        <v>572</v>
       </c>
       <c r="K56" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L56" t="s">
-        <v>517</v>
+        <v>573</v>
       </c>
       <c r="M56" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="N56" t="s">
-        <v>518</v>
+        <v>574</v>
       </c>
       <c r="O56" t="s">
-        <v>519</v>
+        <v>575</v>
       </c>
       <c r="P56" t="s">
-        <v>520</v>
+        <v>576</v>
       </c>
       <c r="R56" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S56" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="T56" t="s">
-        <v>521</v>
+        <v>577</v>
+      </c>
+      <c r="V56">
+        <v>55</v>
+      </c>
+      <c r="W56" t="s">
+        <v>578</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:23">
       <c r="A57">
         <v>2492155</v>
       </c>
       <c r="B57" t="s">
-        <v>522</v>
+        <v>579</v>
       </c>
       <c r="C57" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D57" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="E57" t="s">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="F57" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G57">
         <v>12</v>
@@ -6676,60 +6736,63 @@
         <v>21</v>
       </c>
       <c r="I57" t="s">
-        <v>524</v>
+        <v>581</v>
       </c>
       <c r="J57" t="s">
-        <v>525</v>
+        <v>582</v>
       </c>
       <c r="K57" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L57" t="s">
-        <v>526</v>
+        <v>583</v>
       </c>
       <c r="M57" t="s">
-        <v>527</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>529</v>
+        <v>584</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>586</v>
       </c>
       <c r="P57" t="s">
-        <v>530</v>
+        <v>587</v>
       </c>
       <c r="R57" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S57" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="T57" t="s">
-        <v>531</v>
+        <v>588</v>
       </c>
       <c r="V57">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="W57" t="s">
+        <v>589</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:23">
       <c r="A58">
         <v>1259265</v>
       </c>
       <c r="B58" t="s">
-        <v>532</v>
+        <v>590</v>
       </c>
       <c r="C58" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="D58" t="s">
-        <v>533</v>
+        <v>591</v>
       </c>
       <c r="E58" t="s">
-        <v>534</v>
+        <v>592</v>
       </c>
       <c r="F58" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="G58">
         <v>8</v>
@@ -6741,54 +6804,60 @@
         <v>65</v>
       </c>
       <c r="J58" t="s">
-        <v>535</v>
+        <v>593</v>
       </c>
       <c r="K58" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L58" t="s">
-        <v>536</v>
+        <v>594</v>
       </c>
       <c r="M58" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="N58" t="s">
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="O58" t="s">
-        <v>538</v>
+        <v>596</v>
       </c>
       <c r="P58" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="R58" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S58" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="T58" t="s">
-        <v>540</v>
+        <v>598</v>
+      </c>
+      <c r="V58">
+        <v>57</v>
+      </c>
+      <c r="W58" t="s">
+        <v>599</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:23">
       <c r="A59">
         <v>1168112</v>
       </c>
       <c r="B59" t="s">
-        <v>522</v>
+        <v>579</v>
       </c>
       <c r="C59" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D59" t="s">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="E59" t="s">
-        <v>542</v>
+        <v>601</v>
       </c>
       <c r="F59" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G59">
         <v>8</v>
@@ -6797,57 +6866,63 @@
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>543</v>
+        <v>602</v>
       </c>
       <c r="J59" t="s">
-        <v>544</v>
+        <v>603</v>
       </c>
       <c r="K59" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L59" t="s">
-        <v>545</v>
+        <v>604</v>
       </c>
       <c r="M59" t="s">
-        <v>493</v>
-      </c>
-      <c r="N59" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="O59" s="1" t="s">
-        <v>546</v>
+      <c r="N59" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>605</v>
       </c>
       <c r="P59" t="s">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="R59" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S59" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="T59" t="s">
-        <v>548</v>
+        <v>607</v>
+      </c>
+      <c r="V59">
+        <v>58</v>
+      </c>
+      <c r="W59" t="s">
+        <v>608</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:23">
       <c r="A60">
         <v>767290</v>
       </c>
       <c r="B60" t="s">
-        <v>522</v>
+        <v>579</v>
       </c>
       <c r="C60" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="D60" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="E60" t="s">
-        <v>549</v>
+        <v>609</v>
       </c>
       <c r="F60" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="G60">
         <v>4</v>
@@ -6856,57 +6931,63 @@
         <v>21</v>
       </c>
       <c r="I60" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="J60" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="K60" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L60" t="s">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="M60" t="s">
-        <v>551</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>553</v>
+        <v>611</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>613</v>
       </c>
       <c r="P60" t="s">
-        <v>554</v>
+        <v>614</v>
       </c>
       <c r="R60" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S60" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="T60" t="s">
-        <v>555</v>
+        <v>615</v>
+      </c>
+      <c r="V60">
+        <v>59</v>
+      </c>
+      <c r="W60" t="s">
+        <v>616</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:23">
       <c r="A61">
         <v>877423</v>
       </c>
       <c r="B61" t="s">
-        <v>556</v>
+        <v>617</v>
       </c>
       <c r="C61" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="D61" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="E61" t="s">
-        <v>557</v>
+        <v>618</v>
       </c>
       <c r="F61" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="G61">
         <v>11</v>
@@ -6915,37 +6996,43 @@
         <v>19</v>
       </c>
       <c r="I61" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J61" t="s">
-        <v>558</v>
+        <v>619</v>
       </c>
       <c r="K61" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L61" t="s">
-        <v>559</v>
+        <v>620</v>
       </c>
       <c r="M61" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="N61" t="s">
-        <v>560</v>
+        <v>621</v>
       </c>
       <c r="O61" t="s">
-        <v>561</v>
+        <v>622</v>
       </c>
       <c r="P61" t="s">
-        <v>562</v>
+        <v>623</v>
       </c>
       <c r="R61" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="S61" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="T61" t="s">
-        <v>563</v>
+        <v>624</v>
+      </c>
+      <c r="V61">
+        <v>60</v>
+      </c>
+      <c r="W61" t="s">
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -6973,6 +7060,7 @@
     <hyperlink ref="O14" r:id="rId20" display="https://cs.stanford.edu/people/rak248/VG_100K_2/2405857.jpg"/>
     <hyperlink ref="N15" r:id="rId21" display="http://manynames.upf.edu/2415731_3627437_pitcher.png"/>
     <hyperlink ref="N16" r:id="rId22" display="http://manynames.upf.edu/2410095_226061_bird.png" tooltip="http://manynames.upf.edu/2410095_226061_bird.png"/>
+    <hyperlink ref="O16" r:id="rId22" display="http://manynames.upf.edu/2410095_226061_bird.png" tooltip="http://manynames.upf.edu/2410095_226061_bird.png"/>
     <hyperlink ref="N17" r:id="rId23" display="http://manynames.upf.edu/2413428_173748_cat.png" tooltip="http://manynames.upf.edu/2413428_173748_cat.png"/>
     <hyperlink ref="O17" r:id="rId23" display="http://manynames.upf.edu/2413428_173748_cat.png" tooltip="http://manynames.upf.edu/2413428_173748_cat.png"/>
     <hyperlink ref="N18" r:id="rId24" display="http://manynames.upf.edu/2317946_2746869_flower.png"/>
@@ -6995,33 +7083,32 @@
     <hyperlink ref="N30" r:id="rId40" display="http://manynames.upf.edu/2408684_256924_cat.png" tooltip="http://manynames.upf.edu/2408684_256924_cat.png"/>
     <hyperlink ref="O30" r:id="rId40" display="http://manynames.upf.edu/2408684_256924_cat.png" tooltip="http://manynames.upf.edu/2408684_256924_cat.png"/>
     <hyperlink ref="N31" r:id="rId41" display="http://manynames.upf.edu/2355614_2623413_player.png"/>
-    <hyperlink ref="N33" r:id="rId42" display="http://manynames.upf.edu/2338302_2416631_airplane.png" tooltip="http://manynames.upf.edu/2338302_2416631_airplane.png"/>
-    <hyperlink ref="O33" r:id="rId42" display="http://manynames.upf.edu/2338302_2416631_airplane.png" tooltip="http://manynames.upf.edu/2338302_2416631_airplane.png"/>
-    <hyperlink ref="N34" r:id="rId43" display="http://manynames.upf.edu/2408464_261223_airplane.png" tooltip="http://manynames.upf.edu/2408464_261223_airplane.png"/>
-    <hyperlink ref="O34" r:id="rId43" display="http://manynames.upf.edu/2408464_261223_airplane.png" tooltip="http://manynames.upf.edu/2408464_261223_airplane.png"/>
-    <hyperlink ref="N36" r:id="rId44" display="http://manynames.upf.edu/1592406_2377552_building.png"/>
-    <hyperlink ref="N38" r:id="rId45" display="http://manynames.upf.edu/2379457_552679_bed.png"/>
-    <hyperlink ref="O38" r:id="rId46" display="https://cs.stanford.edu/people/rak248/VG_100K_2/2379457.jpg"/>
-    <hyperlink ref="N44" r:id="rId47" display="http://manynames.upf.edu/2335906_961547_van.png" tooltip="http://manynames.upf.edu/2335906_961547_van.png"/>
-    <hyperlink ref="O44" r:id="rId48" display="https://cs.stanford.edu/people/rak248/VG_100K/2335906.jpg"/>
-    <hyperlink ref="N53" r:id="rId49" display="http://manynames.upf.edu/2341773_2075639_boat.png" tooltip="http://manynames.upf.edu/2341773_2075639_boat.png"/>
-    <hyperlink ref="N59" r:id="rId50" display="http://manynames.upf.edu/2399613_1168112_car.png" tooltip="http://manynames.upf.edu/2399613_1168112_car.png"/>
-    <hyperlink ref="O59" r:id="rId50" display="http://manynames.upf.edu/2399613_1168112_car.png" tooltip="http://manynames.upf.edu/2399613_1168112_car.png"/>
-    <hyperlink ref="N60" r:id="rId51" display="http://manynames.upf.edu/2363195_767290_car.png"/>
-    <hyperlink ref="O60" r:id="rId52" display="https://cs.stanford.edu/people/rak248/VG_100K/2363195.jpg"/>
-    <hyperlink ref="O16" r:id="rId22" display="http://manynames.upf.edu/2410095_226061_bird.png" tooltip="http://manynames.upf.edu/2410095_226061_bird.png"/>
-    <hyperlink ref="N32" r:id="rId53" display="http://manynames.upf.edu/2408308_264145_desk.png" tooltip="http://manynames.upf.edu/2408308_264145_desk.png"/>
-    <hyperlink ref="O32" r:id="rId53" display="http://manynames.upf.edu/2408308_264145_desk.png"/>
-    <hyperlink ref="N40" r:id="rId54" display="http://manynames.upf.edu/2407811_273218_cake.png" tooltip="http://manynames.upf.edu/2407811_273218_cake.png"/>
-    <hyperlink ref="N48" r:id="rId55" display="http://manynames.upf.edu/2342092_937444_pasta.png" tooltip="http://manynames.upf.edu/2342092_937444_pasta.png"/>
-    <hyperlink ref="O40" r:id="rId54" display="http://manynames.upf.edu/2407811_273218_cake.png" tooltip="http://manynames.upf.edu/2407811_273218_cake.png"/>
-    <hyperlink ref="N46" r:id="rId56" display="http://manynames.upf.edu/2378920_556533_pizza.png"/>
+    <hyperlink ref="N32" r:id="rId42" display="http://manynames.upf.edu/2408308_264145_desk.png" tooltip="http://manynames.upf.edu/2408308_264145_desk.png"/>
+    <hyperlink ref="O32" r:id="rId42" display="http://manynames.upf.edu/2408308_264145_desk.png"/>
+    <hyperlink ref="N33" r:id="rId43" display="http://manynames.upf.edu/2338302_2416631_airplane.png" tooltip="http://manynames.upf.edu/2338302_2416631_airplane.png"/>
+    <hyperlink ref="O33" r:id="rId43" display="http://manynames.upf.edu/2338302_2416631_airplane.png" tooltip="http://manynames.upf.edu/2338302_2416631_airplane.png"/>
+    <hyperlink ref="N34" r:id="rId44" display="http://manynames.upf.edu/2408464_261223_airplane.png" tooltip="http://manynames.upf.edu/2408464_261223_airplane.png"/>
+    <hyperlink ref="O34" r:id="rId44" display="http://manynames.upf.edu/2408464_261223_airplane.png" tooltip="http://manynames.upf.edu/2408464_261223_airplane.png"/>
+    <hyperlink ref="N36" r:id="rId45" display="http://manynames.upf.edu/1592406_2377552_building.png"/>
+    <hyperlink ref="N38" r:id="rId46" display="http://manynames.upf.edu/2379457_552679_bed.png"/>
+    <hyperlink ref="O38" r:id="rId47" display="https://cs.stanford.edu/people/rak248/VG_100K_2/2379457.jpg"/>
+    <hyperlink ref="N40" r:id="rId48" display="http://manynames.upf.edu/2407811_273218_cake.png" tooltip="http://manynames.upf.edu/2407811_273218_cake.png"/>
+    <hyperlink ref="O40" r:id="rId48" display="http://manynames.upf.edu/2407811_273218_cake.png" tooltip="http://manynames.upf.edu/2407811_273218_cake.png"/>
+    <hyperlink ref="N44" r:id="rId49" display="http://manynames.upf.edu/2335906_961547_van.png" tooltip="http://manynames.upf.edu/2335906_961547_van.png"/>
+    <hyperlink ref="O44" r:id="rId50" display="https://cs.stanford.edu/people/rak248/VG_100K/2335906.jpg"/>
+    <hyperlink ref="N46" r:id="rId51" display="http://manynames.upf.edu/2378920_556533_pizza.png"/>
+    <hyperlink ref="N48" r:id="rId52" display="http://manynames.upf.edu/2342092_937444_pasta.png" tooltip="http://manynames.upf.edu/2342092_937444_pasta.png"/>
+    <hyperlink ref="O48" r:id="rId53" display="https://cs.stanford.edu/people/rak248/VG_100K/2342092.jpg" tooltip="https://cs.stanford.edu/people/rak248/VG_100K/2342092.jpg"/>
+    <hyperlink ref="N50" r:id="rId54" display="http://manynames.upf.edu/2374793_725035_table.png"/>
+    <hyperlink ref="N51" r:id="rId55" display="http://manynames.upf.edu/2380062_1351071_shirt.png"/>
+    <hyperlink ref="N53" r:id="rId56" display="http://manynames.upf.edu/2341773_2075639_boat.png" tooltip="http://manynames.upf.edu/2341773_2075639_boat.png"/>
+    <hyperlink ref="O53" r:id="rId56" display="http://manynames.upf.edu/2341773_2075639_boat.png"/>
     <hyperlink ref="N57" r:id="rId57" display="http://manynames.upf.edu/2334925_2492155_truck.png" tooltip="http://manynames.upf.edu/2334925_2492155_truck.png"/>
-    <hyperlink ref="O48" r:id="rId58" display="https://cs.stanford.edu/people/rak248/VG_100K/2342092.jpg" tooltip="https://cs.stanford.edu/people/rak248/VG_100K/2342092.jpg"/>
-    <hyperlink ref="N50" r:id="rId59" display="http://manynames.upf.edu/2374793_725035_table.png"/>
-    <hyperlink ref="N51" r:id="rId60" display="http://manynames.upf.edu/2380062_1351071_shirt.png"/>
-    <hyperlink ref="O57" r:id="rId61" display="https://cs.stanford.edu/people/rak248/VG_100K/2334925.jpg" tooltip="https://cs.stanford.edu/people/rak248/VG_100K/2334925.jpg"/>
-    <hyperlink ref="O53" r:id="rId49" display="http://manynames.upf.edu/2341773_2075639_boat.png"/>
+    <hyperlink ref="O57" r:id="rId58" display="https://cs.stanford.edu/people/rak248/VG_100K/2334925.jpg" tooltip="https://cs.stanford.edu/people/rak248/VG_100K/2334925.jpg"/>
+    <hyperlink ref="N59" r:id="rId59" display="http://manynames.upf.edu/2399613_1168112_car.png" tooltip="http://manynames.upf.edu/2399613_1168112_car.png"/>
+    <hyperlink ref="O59" r:id="rId59" display="http://manynames.upf.edu/2399613_1168112_car.png" tooltip="http://manynames.upf.edu/2399613_1168112_car.png"/>
+    <hyperlink ref="N60" r:id="rId60" display="http://manynames.upf.edu/2363195_767290_car.png"/>
+    <hyperlink ref="O60" r:id="rId61" display="https://cs.stanford.edu/people/rak248/VG_100K/2363195.jpg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
